--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Yield Per Hectare - Foodgrains.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Yield Per Hectare - Foodgrains.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>Year</t>
   </si>
@@ -37,9 +37,6 @@
     <t xml:space="preserve">2025-26   </t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">2024-25   </t>
   </si>
   <si>
@@ -271,8 +268,8 @@
     <t>Kg / Hectare</t>
   </si>
   <si>
-    <t xml:space="preserve">Note : Data for 2025-26 are based on First Advance Estimates.
-Also see Notes on Tables.
+    <t xml:space="preserve">Note    : Data for 2025-26 are based on Third Advance Estimates.
+              Also see Notes on Tables
 Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India.</t>
   </si>
 </sst>
@@ -480,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:I87"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="14.541796" customWidth="1"/>
@@ -488,12 +485,14 @@
     <col min="5" max="5" width="13.252692" customWidth="1"/>
     <col min="6" max="6" width="13.2374813333333" customWidth="1"/>
     <col min="7" max="8" width="13.2450866666667" customWidth="1"/>
+    <col min="9" max="9" width="68944e-6" customWidth="1"/>
+    <col min="10" max="10" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="15.999" customHeight="1">
       <c r="B2" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
@@ -502,7 +501,7 @@
     <row r="3" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B4" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="6.9329" customHeight="1"/>
@@ -568,27 +567,27 @@
         <v>8</v>
       </c>
       <c r="C9" s="10">
-        <v>2819</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>9</v>
+        <v>2915</v>
+      </c>
+      <c r="D9" s="10">
+        <v>3591</v>
       </c>
       <c r="E9" s="10">
-        <v>2167</v>
+        <v>2733</v>
       </c>
       <c r="F9" s="10">
-        <v>2622</v>
+        <v>3071</v>
       </c>
       <c r="G9" s="10">
-        <v>678</v>
+        <v>957</v>
       </c>
       <c r="H9" s="10">
-        <v>2336</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B10" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="11">
         <v>2929</v>
@@ -611,7 +610,7 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B11" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="10">
         <v>2882</v>
@@ -634,7 +633,7 @@
     </row>
     <row r="12" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B12" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="11">
         <v>2838</v>
@@ -657,7 +656,7 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B13" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="10">
         <v>2797.647447</v>
@@ -680,7 +679,7 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B14" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="11">
         <v>2717</v>
@@ -703,7 +702,7 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B15" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="10">
         <v>2722</v>
@@ -726,7 +725,7 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B16" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="11">
         <v>2638</v>
@@ -749,7 +748,7 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B17" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="10">
         <v>2576</v>
@@ -772,7 +771,7 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B18" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="11">
         <v>2494</v>
@@ -795,7 +794,7 @@
     </row>
     <row r="19" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B19" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="10">
         <v>2400</v>
@@ -818,7 +817,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B20" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C20" s="11">
         <v>2390</v>
@@ -841,7 +840,7 @@
     </row>
     <row r="21" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B21" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" s="10">
         <v>2424</v>
@@ -864,7 +863,7 @@
     </row>
     <row r="22" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B22" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="11">
         <v>2461</v>
@@ -887,7 +886,7 @@
     </row>
     <row r="23" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B23" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="10">
         <v>2393</v>
@@ -910,7 +909,7 @@
     </row>
     <row r="24" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B24" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" s="11">
         <v>2239</v>
@@ -933,7 +932,7 @@
     </row>
     <row r="25" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B25" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" s="10">
         <v>2125</v>
@@ -956,7 +955,7 @@
     </row>
     <row r="26" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B26" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C26" s="11">
         <v>2178</v>
@@ -979,7 +978,7 @@
     </row>
     <row r="27" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B27" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C27" s="10">
         <v>2202</v>
@@ -1002,7 +1001,7 @@
     </row>
     <row r="28" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B28" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="11">
         <v>2131</v>
@@ -1025,7 +1024,7 @@
     </row>
     <row r="29" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B29" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="10">
         <v>2102</v>
@@ -1048,7 +1047,7 @@
     </row>
     <row r="30" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B30" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" s="11">
         <v>1984</v>
@@ -1071,7 +1070,7 @@
     </row>
     <row r="31" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B31" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C31" s="10">
         <v>2077</v>
@@ -1094,7 +1093,7 @@
     </row>
     <row r="32" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B32" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="11">
         <v>1744</v>
@@ -1117,7 +1116,7 @@
     </row>
     <row r="33" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B33" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="10">
         <v>2079</v>
@@ -1140,7 +1139,7 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B34" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="11">
         <v>1901</v>
@@ -1163,7 +1162,7 @@
     </row>
     <row r="35" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B35" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="10">
         <v>1986</v>
@@ -1186,7 +1185,7 @@
     </row>
     <row r="36" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B36" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="11">
         <v>1921</v>
@@ -1209,7 +1208,7 @@
     </row>
     <row r="37" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B37" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="10">
         <v>1900</v>
@@ -1232,7 +1231,7 @@
     </row>
     <row r="38" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B38" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="11">
         <v>1882</v>
@@ -1255,7 +1254,7 @@
     </row>
     <row r="39" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B39" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="10">
         <v>1797</v>
@@ -1278,7 +1277,7 @@
     </row>
     <row r="40" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B40" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="11">
         <v>1911</v>
@@ -1301,7 +1300,7 @@
     </row>
     <row r="41" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B41" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" s="10">
         <v>1888</v>
@@ -1324,7 +1323,7 @@
     </row>
     <row r="42" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B42" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="11">
         <v>1744</v>
@@ -1347,7 +1346,7 @@
     </row>
     <row r="43" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B43" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="10">
         <v>1751</v>
@@ -1370,7 +1369,7 @@
     </row>
     <row r="44" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B44" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C44" s="11">
         <v>1740</v>
@@ -1393,7 +1392,7 @@
     </row>
     <row r="45" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B45" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="10">
         <v>1745</v>
@@ -1416,7 +1415,7 @@
     </row>
     <row r="46" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B46" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="11">
         <v>1689</v>
@@ -1439,7 +1438,7 @@
     </row>
     <row r="47" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B47" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="10">
         <v>1465</v>
@@ -1462,7 +1461,7 @@
     </row>
     <row r="48" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B48" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="11">
         <v>1471</v>
@@ -1485,7 +1484,7 @@
     </row>
     <row r="49" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B49" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" s="10">
         <v>1552</v>
@@ -1508,7 +1507,7 @@
     </row>
     <row r="50" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B50" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" s="11">
         <v>1417</v>
@@ -1531,7 +1530,7 @@
     </row>
     <row r="51" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B51" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C51" s="10">
         <v>1457</v>
@@ -1554,7 +1553,7 @@
     </row>
     <row r="52" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B52" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C52" s="11">
         <v>1231</v>
@@ -1577,7 +1576,7 @@
     </row>
     <row r="53" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B53" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" s="10">
         <v>1308</v>
@@ -1600,7 +1599,7 @@
     </row>
     <row r="54" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B54" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C54" s="11">
         <v>1336</v>
@@ -1623,7 +1622,7 @@
     </row>
     <row r="55" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B55" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C55" s="10">
         <v>1074</v>
@@ -1646,7 +1645,7 @@
     </row>
     <row r="56" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B56" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C56" s="11">
         <v>1328</v>
@@ -1669,7 +1668,7 @@
     </row>
     <row r="57" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B57" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" s="10">
         <v>1308</v>
@@ -1692,7 +1691,7 @@
     </row>
     <row r="58" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B58" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" s="11">
         <v>1089</v>
@@ -1715,7 +1714,7 @@
     </row>
     <row r="59" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B59" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C59" s="10">
         <v>1235</v>
@@ -1738,7 +1737,7 @@
     </row>
     <row r="60" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B60" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C60" s="11">
         <v>1045</v>
@@ -1761,7 +1760,7 @@
     </row>
     <row r="61" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B61" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C61" s="10">
         <v>1151</v>
@@ -1784,7 +1783,7 @@
     </row>
     <row r="62" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B62" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" s="11">
         <v>1070</v>
@@ -1807,7 +1806,7 @@
     </row>
     <row r="63" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B63" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" s="10">
         <v>1141</v>
@@ -1830,7 +1829,7 @@
     </row>
     <row r="64" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B64" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C64" s="11">
         <v>1123</v>
@@ -1853,7 +1852,7 @@
     </row>
     <row r="65" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B65" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C65" s="10">
         <v>1073</v>
@@ -1876,7 +1875,7 @@
     </row>
     <row r="66" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B66" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C66" s="11">
         <v>1076</v>
@@ -1899,7 +1898,7 @@
     </row>
     <row r="67" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B67" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C67" s="10">
         <v>1032</v>
@@ -1922,7 +1921,7 @@
     </row>
     <row r="68" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B68" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" s="11">
         <v>863</v>
@@ -1945,7 +1944,7 @@
     </row>
     <row r="69" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B69" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C69" s="10">
         <v>862</v>
@@ -1968,7 +1967,7 @@
     </row>
     <row r="70" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B70" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C70" s="11">
         <v>1078</v>
@@ -1991,7 +1990,7 @@
     </row>
     <row r="71" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B71" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C71" s="10">
         <v>1033</v>
@@ -2014,7 +2013,7 @@
     </row>
     <row r="72" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B72" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C72" s="11">
         <v>931</v>
@@ -2037,7 +2036,7 @@
     </row>
     <row r="73" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B73" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C73" s="10">
         <v>1028</v>
@@ -2060,7 +2059,7 @@
     </row>
     <row r="74" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B74" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C74" s="11">
         <v>1013</v>
@@ -2083,7 +2082,7 @@
     </row>
     <row r="75" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B75" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C75" s="10">
         <v>937</v>
@@ -2106,7 +2105,7 @@
     </row>
     <row r="76" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B76" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C76" s="11">
         <v>930</v>
@@ -2129,7 +2128,7 @@
     </row>
     <row r="77" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B77" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C77" s="10">
         <v>790</v>
@@ -2152,7 +2151,7 @@
     </row>
     <row r="78" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B78" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C78" s="11">
         <v>900</v>
@@ -2175,7 +2174,7 @@
     </row>
     <row r="79" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B79" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C79" s="10">
         <v>874</v>
@@ -2198,7 +2197,7 @@
     </row>
     <row r="80" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B80" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C80" s="11">
         <v>820</v>
@@ -2221,7 +2220,7 @@
     </row>
     <row r="81" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B81" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C81" s="10">
         <v>902</v>
@@ -2244,7 +2243,7 @@
     </row>
     <row r="82" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B82" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C82" s="11">
         <v>764</v>
@@ -2267,7 +2266,7 @@
     </row>
     <row r="83" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B83" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C83" s="10">
         <v>714</v>
@@ -2290,7 +2289,7 @@
     </row>
     <row r="84" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C84" s="13">
         <v>668</v>
@@ -2312,19 +2311,24 @@
       </c>
     </row>
     <row r="85" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="86" s="1" customFormat="1" ht="83.1948" customHeight="1">
+    <row r="86" s="1" customFormat="1" ht="72.5288" customHeight="1">
       <c r="B86" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
       <c r="E86" s="16"/>
-    </row>
+      <c r="F86" s="16"/>
+      <c r="G86" s="16"/>
+      <c r="H86" s="16"/>
+      <c r="I86" s="16"/>
+    </row>
+    <row r="87" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B86:I86"/>
     <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageSetup paperSize="120" scale="100" orientation="portrait"/>
